--- a/belgeler/Modul4_Okunabilirlik_Hesaplayici.xlsx
+++ b/belgeler/Modul4_Okunabilirlik_Hesaplayici.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>© Ali AKDAĞLI · Tarsus Üniversitesi SBF · Öğretim Üyelerine YZ Eğitimi
+          <t>© Ali AKDAĞLI · Sağlık Bilimleri Fakültesi Öğretim Elemanları için Yapay Zekâ Eğitimi
 Şeker hastalığı ayaklarınıza zarar verebilir. Ayaklarınız acıyı az hissedebilir. Bu yüzden küçük bir yarayı fark etmeyebilirsiniz. Küçük yaralar büyüyebilir. Her gün ayaklarınıza bakın. Ayna kullanın ya da bir yakınınızdan yardım isteyin. Ayaklarınızı ılık suyla yıkayın. Parmak aralarını iyice kurulayın. Rahat ayakkabı giyin. Ayakkabının içini giymeden önce elinizle yoklayın. Şekeriniz iyi olursa yaranız daha çabuk iyileşir. Size verilen özel terliği hep giyin. Bu terlik yaranın üstüne basmanızı önler. Yarada kızarıklık, şişlik, sıcaklık ya da kötü kokulu akıntı varsa hemen hastaneye gidin.</t>
         </is>
       </c>
@@ -676,7 +676,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>© Ali AKDAĞLI · Tarsus Üniversitesi Sağlık Bilimleri Fakültesi · Öğretim Üyelerine YZ Eğitimi</t>
+          <t>© Ali AKDAĞLI · Sağlık Bilimleri Fakültesi Öğretim Elemanları için Yapay Zekâ Eğitimi</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;20 &amp;KBFBFBFAli AKDAĞLI</oddHeader>
-    <oddFooter>&amp;C© Ali AKDAĞLI · Tarsus Üniversitesi SBF YZ Eğitimi</oddFooter>
+    <oddFooter>&amp;C© Ali AKDAĞLI · Sağlık Bilimleri Fakültesi Öğretim Elemanları için Yapay Zekâ Eğitimi</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -820,7 +820,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;20 &amp;KBFBFBFAli AKDAĞLI</oddHeader>
-    <oddFooter>&amp;C© Ali AKDAĞLI · Tarsus Üniversitesi SBF YZ Eğitimi</oddFooter>
+    <oddFooter>&amp;C© Ali AKDAĞLI · Sağlık Bilimleri Fakültesi Öğretim Elemanları için Yapay Zekâ Eğitimi</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
